--- a/main/ig/StructureDefinition-as-dr-device.xlsx
+++ b/main/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:10:07+00:00</t>
+    <t>2026-09-22T15:44:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
